--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -2316,7 +2316,7 @@
       <c r="N29" s="7" t="inlineStr">
         <is>
           <t>pos 63
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="O29" s="7" t="inlineStr">
@@ -2370,11 +2370,7 @@
       <c r="K30" s="9" t="inlineStr"/>
       <c r="L30" s="9" t="inlineStr"/>
       <c r="M30" s="9" t="inlineStr"/>
-      <c r="N30" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="N30" s="9" t="inlineStr"/>
       <c r="O30" s="9" t="inlineStr"/>
       <c r="P30" s="9" t="inlineStr"/>
     </row>
@@ -2416,11 +2412,7 @@
       <c r="K31" s="9" t="inlineStr"/>
       <c r="L31" s="9" t="inlineStr"/>
       <c r="M31" s="9" t="inlineStr"/>
-      <c r="N31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="N31" s="9" t="inlineStr"/>
       <c r="O31" s="9" t="inlineStr"/>
       <c r="P31" s="9" t="inlineStr"/>
     </row>
@@ -3381,7 +3373,7 @@
       <c r="N48" s="7" t="inlineStr">
         <is>
           <t>pos 63
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
@@ -3431,11 +3423,7 @@
       </c>
       <c r="L49" s="9" t="inlineStr"/>
       <c r="M49" s="9" t="inlineStr"/>
-      <c r="N49" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="N49" s="9" t="inlineStr"/>
       <c r="O49" s="9" t="inlineStr"/>
       <c r="P49" s="9" t="inlineStr"/>
     </row>
@@ -3473,11 +3461,7 @@
       </c>
       <c r="L50" s="9" t="inlineStr"/>
       <c r="M50" s="9" t="inlineStr"/>
-      <c r="N50" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="N50" s="9" t="inlineStr"/>
       <c r="O50" s="9" t="inlineStr"/>
       <c r="P50" s="9" t="inlineStr"/>
     </row>
@@ -4073,7 +4057,7 @@
       <c r="N61" s="7" t="inlineStr">
         <is>
           <t>pos 63
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
@@ -4115,11 +4099,7 @@
       <c r="K62" s="9" t="inlineStr"/>
       <c r="L62" s="9" t="inlineStr"/>
       <c r="M62" s="9" t="inlineStr"/>
-      <c r="N62" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="N62" s="9" t="inlineStr"/>
       <c r="O62" s="9" t="inlineStr"/>
       <c r="P62" s="9" t="inlineStr"/>
     </row>
@@ -7006,7 +6986,7 @@
       <c r="C115" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -7073,7 +7053,7 @@
       <c r="O115" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
       <c r="P115" s="7" t="inlineStr">
@@ -7090,7 +7070,11 @@
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr"/>
-      <c r="C116" s="9" t="inlineStr"/>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="D116" s="9" t="inlineStr"/>
       <c r="E116" s="9" t="inlineStr">
         <is>
@@ -7110,7 +7094,11 @@
         </is>
       </c>
       <c r="N116" s="9" t="inlineStr"/>
-      <c r="O116" s="9" t="inlineStr"/>
+      <c r="O116" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
       <c r="P116" s="9" t="inlineStr"/>
     </row>
     <row r="117" ht="30" customHeight="1">
@@ -7128,7 +7116,7 @@
       <c r="C117" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -7195,7 +7183,7 @@
       <c r="O117" s="7" t="inlineStr">
         <is>
           <t>pos 50
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
       <c r="P117" s="7" t="inlineStr">
@@ -7212,7 +7200,11 @@
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr"/>
-      <c r="C118" s="9" t="inlineStr"/>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
       <c r="D118" s="9" t="inlineStr"/>
       <c r="E118" s="9" t="inlineStr"/>
       <c r="F118" s="9" t="inlineStr"/>
@@ -7224,7 +7216,11 @@
       <c r="L118" s="9" t="inlineStr"/>
       <c r="M118" s="9" t="inlineStr"/>
       <c r="N118" s="9" t="inlineStr"/>
-      <c r="O118" s="9" t="inlineStr"/>
+      <c r="O118" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
       <c r="P118" s="9" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
@@ -7248,13 +7244,13 @@
       <c r="D119" s="7" t="inlineStr">
         <is>
           <t>pos 54
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
           <t>pos 55
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
@@ -7327,8 +7323,16 @@
       </c>
       <c r="B120" s="9" t="inlineStr"/>
       <c r="C120" s="9" t="inlineStr"/>
-      <c r="D120" s="9" t="inlineStr"/>
-      <c r="E120" s="9" t="inlineStr"/>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="F120" s="9" t="inlineStr"/>
       <c r="G120" s="9" t="inlineStr"/>
       <c r="H120" s="9" t="inlineStr"/>
@@ -7586,7 +7590,7 @@
       <c r="C126" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -7653,7 +7657,7 @@
       <c r="O126" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
       <c r="P126" s="7" t="inlineStr">
@@ -7670,7 +7674,11 @@
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr"/>
-      <c r="C127" s="9" t="inlineStr"/>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>LCtrl</t>
+        </is>
+      </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
           <t>🖱右</t>
@@ -7698,7 +7706,11 @@
           <t>🖱右</t>
         </is>
       </c>
-      <c r="O127" s="9" t="inlineStr"/>
+      <c r="O127" s="9" t="inlineStr">
+        <is>
+          <t>RCtrl</t>
+        </is>
+      </c>
       <c r="P127" s="9" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
@@ -7716,7 +7728,7 @@
       <c r="C128" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -7783,7 +7795,7 @@
       <c r="O128" s="7" t="inlineStr">
         <is>
           <t>pos 50
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
       <c r="P128" s="7" t="inlineStr">
@@ -7800,7 +7812,11 @@
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr"/>
-      <c r="C129" s="9" t="inlineStr"/>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>LShift</t>
+        </is>
+      </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
           <t>🖱進</t>
@@ -7828,7 +7844,11 @@
           <t>🖱進</t>
         </is>
       </c>
-      <c r="O129" s="9" t="inlineStr"/>
+      <c r="O129" s="9" t="inlineStr">
+        <is>
+          <t>RShift</t>
+        </is>
+      </c>
       <c r="P129" s="9" t="inlineStr"/>
     </row>
     <row r="130" ht="30" customHeight="1">
@@ -7852,13 +7872,13 @@
       <c r="D130" s="7" t="inlineStr">
         <is>
           <t>pos 54
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
           <t>pos 55
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
@@ -7931,8 +7951,16 @@
       </c>
       <c r="B131" s="9" t="inlineStr"/>
       <c r="C131" s="9" t="inlineStr"/>
-      <c r="D131" s="9" t="inlineStr"/>
-      <c r="E131" s="9" t="inlineStr"/>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>LWin</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>LAlt</t>
+        </is>
+      </c>
       <c r="F131" s="9" t="inlineStr"/>
       <c r="G131" s="9" t="inlineStr"/>
       <c r="H131" s="9" t="inlineStr"/>
@@ -9746,7 +9774,7 @@
       <c r="N29" s="7" t="inlineStr">
         <is>
           <t>pos 63
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="O29" s="7" t="inlineStr">
@@ -9800,11 +9828,7 @@
       <c r="K30" s="9" t="inlineStr"/>
       <c r="L30" s="9" t="inlineStr"/>
       <c r="M30" s="9" t="inlineStr"/>
-      <c r="N30" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="N30" s="9" t="inlineStr"/>
       <c r="O30" s="9" t="inlineStr"/>
       <c r="P30" s="9" t="inlineStr"/>
     </row>
@@ -9846,11 +9870,7 @@
       <c r="K31" s="9" t="inlineStr"/>
       <c r="L31" s="9" t="inlineStr"/>
       <c r="M31" s="9" t="inlineStr"/>
-      <c r="N31" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="N31" s="9" t="inlineStr"/>
       <c r="O31" s="9" t="inlineStr"/>
       <c r="P31" s="9" t="inlineStr"/>
     </row>
@@ -10846,7 +10866,7 @@
       <c r="N48" s="7" t="inlineStr">
         <is>
           <t>pos 63
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="O48" s="7" t="inlineStr">
@@ -10896,11 +10916,7 @@
       </c>
       <c r="L49" s="9" t="inlineStr"/>
       <c r="M49" s="9" t="inlineStr"/>
-      <c r="N49" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="N49" s="9" t="inlineStr"/>
       <c r="O49" s="9" t="inlineStr"/>
       <c r="P49" s="9" t="inlineStr"/>
     </row>
@@ -10938,11 +10954,7 @@
       </c>
       <c r="L50" s="9" t="inlineStr"/>
       <c r="M50" s="9" t="inlineStr"/>
-      <c r="N50" s="9" t="inlineStr">
-        <is>
-          <t>〃</t>
-        </is>
-      </c>
+      <c r="N50" s="9" t="inlineStr"/>
       <c r="O50" s="9" t="inlineStr"/>
       <c r="P50" s="9" t="inlineStr"/>
     </row>
@@ -11550,7 +11562,7 @@
       <c r="N61" s="7" t="inlineStr">
         <is>
           <t>pos 63
-&amp;trans</t>
+&amp;none</t>
         </is>
       </c>
       <c r="O61" s="7" t="inlineStr">
@@ -11592,11 +11604,7 @@
       <c r="K62" s="9" t="inlineStr"/>
       <c r="L62" s="9" t="inlineStr"/>
       <c r="M62" s="9" t="inlineStr"/>
-      <c r="N62" s="9" t="inlineStr">
-        <is>
-          <t>▽</t>
-        </is>
-      </c>
+      <c r="N62" s="9" t="inlineStr"/>
       <c r="O62" s="9" t="inlineStr"/>
       <c r="P62" s="9" t="inlineStr"/>
     </row>
@@ -14488,7 +14496,7 @@
       <c r="C115" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -14555,7 +14563,7 @@
       <c r="O115" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
       <c r="P115" s="7" t="inlineStr">
@@ -14572,7 +14580,11 @@
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr"/>
-      <c r="C116" s="9" t="inlineStr"/>
+      <c r="C116" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="D116" s="9" t="inlineStr"/>
       <c r="E116" s="9" t="inlineStr">
         <is>
@@ -14592,7 +14604,11 @@
         </is>
       </c>
       <c r="N116" s="9" t="inlineStr"/>
-      <c r="O116" s="9" t="inlineStr"/>
+      <c r="O116" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
       <c r="P116" s="9" t="inlineStr"/>
     </row>
     <row r="117" ht="30" customHeight="1">
@@ -14610,7 +14626,7 @@
       <c r="C117" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -14677,7 +14693,7 @@
       <c r="O117" s="7" t="inlineStr">
         <is>
           <t>pos 50
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
       <c r="P117" s="7" t="inlineStr">
@@ -14694,7 +14710,11 @@
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr"/>
-      <c r="C118" s="9" t="inlineStr"/>
+      <c r="C118" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
       <c r="D118" s="9" t="inlineStr"/>
       <c r="E118" s="9" t="inlineStr"/>
       <c r="F118" s="9" t="inlineStr"/>
@@ -14706,7 +14726,11 @@
       <c r="L118" s="9" t="inlineStr"/>
       <c r="M118" s="9" t="inlineStr"/>
       <c r="N118" s="9" t="inlineStr"/>
-      <c r="O118" s="9" t="inlineStr"/>
+      <c r="O118" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
       <c r="P118" s="9" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
@@ -14730,13 +14754,13 @@
       <c r="D119" s="7" t="inlineStr">
         <is>
           <t>pos 54
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
           <t>pos 55
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
@@ -14809,8 +14833,16 @@
       </c>
       <c r="B120" s="9" t="inlineStr"/>
       <c r="C120" s="9" t="inlineStr"/>
-      <c r="D120" s="9" t="inlineStr"/>
-      <c r="E120" s="9" t="inlineStr"/>
+      <c r="D120" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="E120" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="F120" s="9" t="inlineStr"/>
       <c r="G120" s="9" t="inlineStr"/>
       <c r="H120" s="9" t="inlineStr"/>
@@ -15068,7 +15100,7 @@
       <c r="C126" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;none</t>
+&amp;kp LCTRL</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -15135,7 +15167,7 @@
       <c r="O126" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp RCTRL</t>
         </is>
       </c>
       <c r="P126" s="7" t="inlineStr">
@@ -15152,7 +15184,11 @@
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr"/>
-      <c r="C127" s="9" t="inlineStr"/>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LCTRL</t>
+        </is>
+      </c>
       <c r="D127" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB2</t>
@@ -15180,7 +15216,11 @@
           <t>&amp;mkp MB2</t>
         </is>
       </c>
-      <c r="O127" s="9" t="inlineStr"/>
+      <c r="O127" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RCTRL</t>
+        </is>
+      </c>
       <c r="P127" s="9" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
@@ -15198,7 +15238,7 @@
       <c r="C128" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;none</t>
+&amp;kp LEFT_SHIFT</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -15265,7 +15305,7 @@
       <c r="O128" s="7" t="inlineStr">
         <is>
           <t>pos 50
-&amp;none</t>
+&amp;kp RIGHT_SHIFT</t>
         </is>
       </c>
       <c r="P128" s="7" t="inlineStr">
@@ -15282,7 +15322,11 @@
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr"/>
-      <c r="C129" s="9" t="inlineStr"/>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_SHIFT</t>
+        </is>
+      </c>
       <c r="D129" s="9" t="inlineStr">
         <is>
           <t>&amp;mkp MB5</t>
@@ -15310,7 +15354,11 @@
           <t>&amp;mkp MB5</t>
         </is>
       </c>
-      <c r="O129" s="9" t="inlineStr"/>
+      <c r="O129" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp RIGHT_SHIFT</t>
+        </is>
+      </c>
       <c r="P129" s="9" t="inlineStr"/>
     </row>
     <row r="130" ht="30" customHeight="1">
@@ -15334,13 +15382,13 @@
       <c r="D130" s="7" t="inlineStr">
         <is>
           <t>pos 54
-&amp;none</t>
+&amp;kp LEFT_WIN</t>
         </is>
       </c>
       <c r="E130" s="7" t="inlineStr">
         <is>
           <t>pos 55
-&amp;none</t>
+&amp;kp LEFT_ALT</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
@@ -15413,8 +15461,16 @@
       </c>
       <c r="B131" s="9" t="inlineStr"/>
       <c r="C131" s="9" t="inlineStr"/>
-      <c r="D131" s="9" t="inlineStr"/>
-      <c r="E131" s="9" t="inlineStr"/>
+      <c r="D131" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_WIN</t>
+        </is>
+      </c>
+      <c r="E131" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp LEFT_ALT</t>
+        </is>
+      </c>
       <c r="F131" s="9" t="inlineStr"/>
       <c r="G131" s="9" t="inlineStr"/>
       <c r="H131" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -6986,7 +6986,7 @@
       <c r="C115" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;kp LCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -7053,7 +7053,7 @@
       <c r="O115" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;kp RCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="P115" s="7" t="inlineStr">
@@ -7072,7 +7072,7 @@
       <c r="B116" s="9" t="inlineStr"/>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>LCtrl</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr"/>
@@ -7096,7 +7096,7 @@
       <c r="N116" s="9" t="inlineStr"/>
       <c r="O116" s="9" t="inlineStr">
         <is>
-          <t>RCtrl</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="P116" s="9" t="inlineStr"/>
@@ -7116,7 +7116,7 @@
       <c r="C117" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;kp LEFT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -7183,7 +7183,7 @@
       <c r="O117" s="7" t="inlineStr">
         <is>
           <t>pos 50
-&amp;kp RIGHT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="P117" s="7" t="inlineStr">
@@ -7202,7 +7202,7 @@
       <c r="B118" s="9" t="inlineStr"/>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>LShift</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr"/>
@@ -7218,7 +7218,7 @@
       <c r="N118" s="9" t="inlineStr"/>
       <c r="O118" s="9" t="inlineStr">
         <is>
-          <t>RShift</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="P118" s="9" t="inlineStr"/>
@@ -7244,13 +7244,13 @@
       <c r="D119" s="7" t="inlineStr">
         <is>
           <t>pos 54
-&amp;kp LEFT_WIN</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
           <t>pos 55
-&amp;kp LEFT_ALT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
@@ -7325,12 +7325,12 @@
       <c r="C120" s="9" t="inlineStr"/>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>LWin</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>LAlt</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>
@@ -14496,7 +14496,7 @@
       <c r="C115" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;kp LCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -14563,7 +14563,7 @@
       <c r="O115" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;kp RCTRL</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="P115" s="7" t="inlineStr">
@@ -14582,7 +14582,7 @@
       <c r="B116" s="9" t="inlineStr"/>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LCTRL</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr"/>
@@ -14606,7 +14606,7 @@
       <c r="N116" s="9" t="inlineStr"/>
       <c r="O116" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RCTRL</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="P116" s="9" t="inlineStr"/>
@@ -14626,7 +14626,7 @@
       <c r="C117" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;kp LEFT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
@@ -14693,7 +14693,7 @@
       <c r="O117" s="7" t="inlineStr">
         <is>
           <t>pos 50
-&amp;kp RIGHT_SHIFT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="P117" s="7" t="inlineStr">
@@ -14712,7 +14712,7 @@
       <c r="B118" s="9" t="inlineStr"/>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_SHIFT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr"/>
@@ -14728,7 +14728,7 @@
       <c r="N118" s="9" t="inlineStr"/>
       <c r="O118" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp RIGHT_SHIFT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="P118" s="9" t="inlineStr"/>
@@ -14754,13 +14754,13 @@
       <c r="D119" s="7" t="inlineStr">
         <is>
           <t>pos 54
-&amp;kp LEFT_WIN</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
           <t>pos 55
-&amp;kp LEFT_ALT</t>
+&amp;trans</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
@@ -14835,12 +14835,12 @@
       <c r="C120" s="9" t="inlineStr"/>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_WIN</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="E120" s="9" t="inlineStr">
         <is>
-          <t>&amp;kp LEFT_ALT</t>
+          <t>▽</t>
         </is>
       </c>
       <c r="F120" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -1432,7 +1432,7 @@
       <c r="M15" s="7" t="inlineStr">
         <is>
           <t>pos 62
-&amp;none</t>
+&amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
@@ -1503,7 +1503,11 @@
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>L7</t>
+        </is>
+      </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
           <t>L6</t>
@@ -1565,7 +1569,11 @@
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr"/>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
           <t>〃</t>
@@ -8890,7 +8898,7 @@
       <c r="M15" s="7" t="inlineStr">
         <is>
           <t>pos 62
-&amp;none</t>
+&amp;mo BLUETOOTH</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
@@ -8961,7 +8969,11 @@
         </is>
       </c>
       <c r="L16" s="9" t="inlineStr"/>
-      <c r="M16" s="9" t="inlineStr"/>
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>&amp;mo BLUETOOTH</t>
+        </is>
+      </c>
       <c r="N16" s="9" t="inlineStr">
         <is>
           <t>&amp;mo FUNCTION</t>
@@ -9023,7 +9035,11 @@
         </is>
       </c>
       <c r="L17" s="9" t="inlineStr"/>
-      <c r="M17" s="9" t="inlineStr"/>
+      <c r="M17" s="9" t="inlineStr">
+        <is>
+          <t>〃</t>
+        </is>
+      </c>
       <c r="N17" s="9" t="inlineStr">
         <is>
           <t>〃</t>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5798,7 +5798,7 @@
       <c r="C93" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;none</t>
+&amp;kp CAPSLOCK</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -5810,19 +5810,19 @@
       <c r="E93" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
           <t>pos 28
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -5865,7 +5865,7 @@
       <c r="O93" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
@@ -5882,15 +5882,31 @@
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr"/>
-      <c r="C94" s="9" t="inlineStr"/>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>CAPSLOCK</t>
+        </is>
+      </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
           <t>リセット</t>
         </is>
       </c>
-      <c r="E94" s="9" t="inlineStr"/>
-      <c r="F94" s="9" t="inlineStr"/>
-      <c r="G94" s="9" t="inlineStr"/>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="H94" s="9" t="inlineStr"/>
       <c r="I94" s="9" t="inlineStr"/>
       <c r="J94" s="9" t="inlineStr"/>
@@ -5902,7 +5918,11 @@
           <t>リセット</t>
         </is>
       </c>
-      <c r="O94" s="9" t="inlineStr"/>
+      <c r="O94" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
       <c r="P94" s="9" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
@@ -5920,7 +5940,7 @@
       <c r="C95" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -5932,7 +5952,7 @@
       <c r="E95" s="7" t="inlineStr">
         <is>
           <t>pos 41
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -5987,7 +6007,7 @@
       <c r="O95" s="7" t="inlineStr">
         <is>
           <t>pos 50
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
@@ -6004,9 +6024,17 @@
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr"/>
-      <c r="C96" s="9" t="inlineStr"/>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>K_APP</t>
+        </is>
+      </c>
       <c r="D96" s="9" t="inlineStr"/>
-      <c r="E96" s="9" t="inlineStr"/>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
       <c r="F96" s="9" t="inlineStr"/>
       <c r="G96" s="9" t="inlineStr">
         <is>
@@ -6024,7 +6052,11 @@
       <c r="L96" s="9" t="inlineStr"/>
       <c r="M96" s="9" t="inlineStr"/>
       <c r="N96" s="9" t="inlineStr"/>
-      <c r="O96" s="9" t="inlineStr"/>
+      <c r="O96" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
       <c r="P96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
@@ -13316,7 +13348,7 @@
       <c r="C93" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;none</t>
+&amp;kp CAPSLOCK</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
@@ -13328,19 +13360,19 @@
       <c r="E93" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
           <t>pos 28
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -13383,7 +13415,7 @@
       <c r="O93" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
@@ -13400,15 +13432,31 @@
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr"/>
-      <c r="C94" s="9" t="inlineStr"/>
+      <c r="C94" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp CAPSLOCK</t>
+        </is>
+      </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="E94" s="9" t="inlineStr"/>
-      <c r="F94" s="9" t="inlineStr"/>
-      <c r="G94" s="9" t="inlineStr"/>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="H94" s="9" t="inlineStr"/>
       <c r="I94" s="9" t="inlineStr"/>
       <c r="J94" s="9" t="inlineStr"/>
@@ -13420,7 +13468,11 @@
           <t>&amp;sys_reset</t>
         </is>
       </c>
-      <c r="O94" s="9" t="inlineStr"/>
+      <c r="O94" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F11</t>
+        </is>
+      </c>
       <c r="P94" s="9" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
@@ -13438,7 +13490,7 @@
       <c r="C95" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -13450,7 +13502,7 @@
       <c r="E95" s="7" t="inlineStr">
         <is>
           <t>pos 41
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -13505,7 +13557,7 @@
       <c r="O95" s="7" t="inlineStr">
         <is>
           <t>pos 50
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
@@ -13522,9 +13574,17 @@
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr"/>
-      <c r="C96" s="9" t="inlineStr"/>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp K_APP</t>
+        </is>
+      </c>
       <c r="D96" s="9" t="inlineStr"/>
-      <c r="E96" s="9" t="inlineStr"/>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp INSERT</t>
+        </is>
+      </c>
       <c r="F96" s="9" t="inlineStr"/>
       <c r="G96" s="9" t="inlineStr">
         <is>
@@ -13542,7 +13602,11 @@
       <c r="L96" s="9" t="inlineStr"/>
       <c r="M96" s="9" t="inlineStr"/>
       <c r="N96" s="9" t="inlineStr"/>
-      <c r="O96" s="9" t="inlineStr"/>
+      <c r="O96" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F12</t>
+        </is>
+      </c>
       <c r="P96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5798,13 +5798,13 @@
       <c r="C93" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;kp CAPSLOCK</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -5859,7 +5859,7 @@
       <c r="N93" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="O93" s="7" t="inlineStr">
@@ -5882,16 +5882,8 @@
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr"/>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>CAPSLOCK</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
+      <c r="C94" s="9" t="inlineStr"/>
+      <c r="D94" s="9" t="inlineStr"/>
       <c r="E94" s="9" t="inlineStr">
         <is>
           <t>PRINTSCREEN</t>
@@ -5913,11 +5905,7 @@
       <c r="K94" s="9" t="inlineStr"/>
       <c r="L94" s="9" t="inlineStr"/>
       <c r="M94" s="9" t="inlineStr"/>
-      <c r="N94" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
+      <c r="N94" s="9" t="inlineStr"/>
       <c r="O94" s="9" t="inlineStr">
         <is>
           <t>F11</t>
@@ -5964,7 +5952,7 @@
       <c r="G95" s="7" t="inlineStr">
         <is>
           <t>pos 43
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -5983,7 +5971,7 @@
       <c r="K95" s="7" t="inlineStr">
         <is>
           <t>pos 46
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -6036,19 +6024,11 @@
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr"/>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
       <c r="I96" s="9" t="inlineStr"/>
       <c r="J96" s="9" t="inlineStr"/>
-      <c r="K96" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="K96" s="9" t="inlineStr"/>
       <c r="L96" s="9" t="inlineStr"/>
       <c r="M96" s="9" t="inlineStr"/>
       <c r="N96" s="9" t="inlineStr"/>
@@ -13348,13 +13328,13 @@
       <c r="C93" s="7" t="inlineStr">
         <is>
           <t>pos 25
-&amp;kp CAPSLOCK</t>
+&amp;none</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -13409,7 +13389,7 @@
       <c r="N93" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="O93" s="7" t="inlineStr">
@@ -13432,16 +13412,8 @@
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr"/>
-      <c r="C94" s="9" t="inlineStr">
-        <is>
-          <t>&amp;kp CAPSLOCK</t>
-        </is>
-      </c>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
+      <c r="C94" s="9" t="inlineStr"/>
+      <c r="D94" s="9" t="inlineStr"/>
       <c r="E94" s="9" t="inlineStr">
         <is>
           <t>&amp;kp PRINTSCREEN</t>
@@ -13463,11 +13435,7 @@
       <c r="K94" s="9" t="inlineStr"/>
       <c r="L94" s="9" t="inlineStr"/>
       <c r="M94" s="9" t="inlineStr"/>
-      <c r="N94" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
+      <c r="N94" s="9" t="inlineStr"/>
       <c r="O94" s="9" t="inlineStr">
         <is>
           <t>&amp;kp F11</t>
@@ -13514,7 +13482,7 @@
       <c r="G95" s="7" t="inlineStr">
         <is>
           <t>pos 43
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -13533,7 +13501,7 @@
       <c r="K95" s="7" t="inlineStr">
         <is>
           <t>pos 46
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -13586,19 +13554,11 @@
         </is>
       </c>
       <c r="F96" s="9" t="inlineStr"/>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
       <c r="I96" s="9" t="inlineStr"/>
       <c r="J96" s="9" t="inlineStr"/>
-      <c r="K96" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="K96" s="9" t="inlineStr"/>
       <c r="L96" s="9" t="inlineStr"/>
       <c r="M96" s="9" t="inlineStr"/>
       <c r="N96" s="9" t="inlineStr"/>

--- a/KEYMAP.xlsx
+++ b/KEYMAP.xlsx
@@ -5804,25 +5804,25 @@
       <c r="D93" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
           <t>pos 28
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -5859,13 +5859,13 @@
       <c r="N93" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
@@ -5883,26 +5883,34 @@
       </c>
       <c r="B94" s="9" t="inlineStr"/>
       <c r="C94" s="9" t="inlineStr"/>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr"/>
-      <c r="F94" s="9" t="inlineStr"/>
-      <c r="G94" s="9" t="inlineStr"/>
+      <c r="D94" s="9" t="inlineStr"/>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="H94" s="9" t="inlineStr"/>
       <c r="I94" s="9" t="inlineStr"/>
       <c r="J94" s="9" t="inlineStr"/>
       <c r="K94" s="9" t="inlineStr"/>
       <c r="L94" s="9" t="inlineStr"/>
       <c r="M94" s="9" t="inlineStr"/>
-      <c r="N94" s="9" t="inlineStr">
-        <is>
-          <t>リセット</t>
-        </is>
-      </c>
-      <c r="O94" s="9" t="inlineStr"/>
+      <c r="N94" s="9" t="inlineStr"/>
+      <c r="O94" s="9" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
       <c r="P94" s="9" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
@@ -5920,7 +5928,7 @@
       <c r="C95" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -5932,7 +5940,7 @@
       <c r="E95" s="7" t="inlineStr">
         <is>
           <t>pos 41
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -5944,7 +5952,7 @@
       <c r="G95" s="7" t="inlineStr">
         <is>
           <t>pos 43
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -5963,7 +5971,7 @@
       <c r="K95" s="7" t="inlineStr">
         <is>
           <t>pos 46
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -5987,7 +5995,7 @@
       <c r="O95" s="7" t="inlineStr">
         <is>
           <t>pos 50
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
@@ -6004,27 +6012,31 @@
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr"/>
-      <c r="C96" s="9" t="inlineStr"/>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>K_APP</t>
+        </is>
+      </c>
       <c r="D96" s="9" t="inlineStr"/>
-      <c r="E96" s="9" t="inlineStr"/>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>INSERT</t>
+        </is>
+      </c>
       <c r="F96" s="9" t="inlineStr"/>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
       <c r="I96" s="9" t="inlineStr"/>
       <c r="J96" s="9" t="inlineStr"/>
-      <c r="K96" s="9" t="inlineStr">
-        <is>
-          <t>ブートローダ</t>
-        </is>
-      </c>
+      <c r="K96" s="9" t="inlineStr"/>
       <c r="L96" s="9" t="inlineStr"/>
       <c r="M96" s="9" t="inlineStr"/>
       <c r="N96" s="9" t="inlineStr"/>
-      <c r="O96" s="9" t="inlineStr"/>
+      <c r="O96" s="9" t="inlineStr">
+        <is>
+          <t>F12</t>
+        </is>
+      </c>
       <c r="P96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
@@ -13322,25 +13334,25 @@
       <c r="D93" s="7" t="inlineStr">
         <is>
           <t>pos 26
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
           <t>pos 27
-&amp;none</t>
+&amp;kp PRINTSCREEN</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
           <t>pos 28
-&amp;none</t>
+&amp;kp SCROLLLOCK</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
           <t>pos 29
-&amp;none</t>
+&amp;kp PAUSE_BREAK</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
@@ -13377,13 +13389,13 @@
       <c r="N93" s="7" t="inlineStr">
         <is>
           <t>pos 35
-&amp;sys_reset</t>
+&amp;none</t>
         </is>
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
           <t>pos 36
-&amp;none</t>
+&amp;kp F11</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
@@ -13401,26 +13413,34 @@
       </c>
       <c r="B94" s="9" t="inlineStr"/>
       <c r="C94" s="9" t="inlineStr"/>
-      <c r="D94" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="E94" s="9" t="inlineStr"/>
-      <c r="F94" s="9" t="inlineStr"/>
-      <c r="G94" s="9" t="inlineStr"/>
+      <c r="D94" s="9" t="inlineStr"/>
+      <c r="E94" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PRINTSCREEN</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp SCROLLLOCK</t>
+        </is>
+      </c>
+      <c r="G94" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp PAUSE_BREAK</t>
+        </is>
+      </c>
       <c r="H94" s="9" t="inlineStr"/>
       <c r="I94" s="9" t="inlineStr"/>
       <c r="J94" s="9" t="inlineStr"/>
       <c r="K94" s="9" t="inlineStr"/>
       <c r="L94" s="9" t="inlineStr"/>
       <c r="M94" s="9" t="inlineStr"/>
-      <c r="N94" s="9" t="inlineStr">
-        <is>
-          <t>&amp;sys_reset</t>
-        </is>
-      </c>
-      <c r="O94" s="9" t="inlineStr"/>
+      <c r="N94" s="9" t="inlineStr"/>
+      <c r="O94" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F11</t>
+        </is>
+      </c>
       <c r="P94" s="9" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
@@ -13438,7 +13458,7 @@
       <c r="C95" s="7" t="inlineStr">
         <is>
           <t>pos 39
-&amp;none</t>
+&amp;kp K_APP</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -13450,7 +13470,7 @@
       <c r="E95" s="7" t="inlineStr">
         <is>
           <t>pos 41
-&amp;none</t>
+&amp;kp INSERT</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -13462,7 +13482,7 @@
       <c r="G95" s="7" t="inlineStr">
         <is>
           <t>pos 43
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
@@ -13481,7 +13501,7 @@
       <c r="K95" s="7" t="inlineStr">
         <is>
           <t>pos 46
-&amp;bootloader</t>
+&amp;none</t>
         </is>
       </c>
       <c r="L95" s="7" t="inlineStr">
@@ -13505,7 +13525,7 @@
       <c r="O95" s="7" t="inlineStr">
         <is>
           <t>pos 50
-&amp;none</t>
+&amp;kp F12</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
@@ -13522,27 +13542,31 @@
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr"/>
-      <c r="C96" s="9" t="inlineStr"/>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp K_APP</t>
+        </is>
+      </c>
       <c r="D96" s="9" t="inlineStr"/>
-      <c r="E96" s="9" t="inlineStr"/>
+      <c r="E96" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp INSERT</t>
+        </is>
+      </c>
       <c r="F96" s="9" t="inlineStr"/>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="G96" s="9" t="inlineStr"/>
       <c r="H96" s="9" t="inlineStr"/>
       <c r="I96" s="9" t="inlineStr"/>
       <c r="J96" s="9" t="inlineStr"/>
-      <c r="K96" s="9" t="inlineStr">
-        <is>
-          <t>&amp;bootloader</t>
-        </is>
-      </c>
+      <c r="K96" s="9" t="inlineStr"/>
       <c r="L96" s="9" t="inlineStr"/>
       <c r="M96" s="9" t="inlineStr"/>
       <c r="N96" s="9" t="inlineStr"/>
-      <c r="O96" s="9" t="inlineStr"/>
+      <c r="O96" s="9" t="inlineStr">
+        <is>
+          <t>&amp;kp F12</t>
+        </is>
+      </c>
       <c r="P96" s="9" t="inlineStr"/>
     </row>
     <row r="97" ht="30" customHeight="1">
